--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -316,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -337,9 +337,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
@@ -451,8 +448,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1166,9 +1163,9 @@
           <t>CodeceptJS + Playwright</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>14 / 17</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>17 / 17</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1370,7 +1367,7 @@
       <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Đơn vị (JUnit)</t>
         </is>
@@ -1381,7 +1378,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -1395,7 +1392,7 @@
       <c r="H25" s="9" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Tích hợp (Postman)</t>
         </is>
@@ -1420,7 +1417,7 @@
       <c r="H26" s="9" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Hệ thống (CodeceptJS)</t>
         </is>
@@ -1433,21 +1430,21 @@
       <c r="C27" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>3</v>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>1 lỗi ứng dụng thật, 2 kịch bản lỗi thời sau khi giao diện đổi</t>
+          <t>Ba kịch bản từng đỏ đều là lỗi ứng dụng thật, nay đã sửa xong</t>
         </is>
       </c>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Tám khiếm khuyết được phát hiện, bảy đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Mười khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
         </is>
       </c>
     </row>
@@ -1495,18 +1492,18 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>BẢNG B5 - DANH SÁCH FILE TEST WHITE-BOX VÀ NỘI DUNG KIỂM THỬ</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="26" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="25" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Tổng hợp tất cả các file test white-box (Unit Test với Mockito) trong dự án CareerCompass</t>
         </is>
@@ -1514,863 +1511,863 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>DANH SÁCH FILE KIỂM THỬ HỘP TRẮNG</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="26" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>File Test</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Class được test</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Nội dung test (Logic White-box)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>GlobalExceptionHandlerTest</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Test 16 nhánh của @ControllerAdvice: giả lập ném Exception (IllegalArgument, DataIntegrity) -&gt; kiểm tra trả về JSON 400/409 hoặc Redirect. Bao phủ cả nhánh laApi(), laThaoTacGhi(), trangQuayVe() (valid/invalid Referer).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>AuthServiceTest</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>AuthService</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Phân nhánh luồng Đăng nhập, Đăng ký: đúng pass, sai pass, tài khoản chưa kích hoạt.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>AuthControllerTest</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>AuthController</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Test endpoint /login, /register: kiểm tra redirect và model attribute.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>PasswordResetServiceTest</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>PasswordResetService</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Nhánh tạo token reset, kiểm tra hết hạn (expired), mã hóa mật khẩu mới.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>CustomUserDetailsServiceTest</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>CustomUserDetailsService</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>Truy vấn CSDL bằng Mockito: user tồn tại / không tồn tại -&gt; UsernameNotFoundException.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>SmtpEmailServiceTest</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>SmtpEmailService</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Nhánh gọi API gửi email thành công hoặc thất bại.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>ActivityLogServiceTest</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>ActivityLogService</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Kiểm tra ghi log hoạt động người dùng khi tương tác hệ thống.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
+      <c r="A13" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>AuthenticatedUserServiceTest</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>AuthenticatedUserService</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Lấy thông tin user đã xác thực từ SecurityContext, phân nhánh user null/valid.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>MarkdownRendererTest</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>MarkdownRenderer</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Chuyển đổi Markdown sang HTML, kiểm tra nhánh input null/empty/valid.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
+      <c r="A15" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>UserProfileServiceTest</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>UserProfileService</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>Logic cập nhật thông tin user, kiểm tra nhánh upload avatar và thay đổi profile.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>HomeControllerTest</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>HomeController</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Test endpoint trang chủ, kiểm tra redirect theo trạng thái đăng nhập.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>DashboardServiceTest</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>DashboardService</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Vòng lặp đếm thống kê số lượng User, Mentor, hiển thị biểu đồ.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>AdminDashboardServiceTest</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>AdminDashboardService</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>Test các vòng lặp đếm thống kê tổng hợp cho trang quản trị.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n">
+      <c r="A19" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C19" s="30" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>AdminUserServiceTest</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>AdminUserService</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>Phân nhánh luồng Block/Unblock tài khoản người dùng.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n">
+      <c r="A20" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>CounselorTemplateServiceTest</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>CounselorTemplateService</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Logic CRUD (Thêm, sửa, xóa) các template tư vấn nghề nghiệp.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n">
+      <c r="A21" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>RoadmapServiceTest</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>RoadmapService</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>File cốt lõi! Test calculatePercent() và isNodeLocked() với đầy đủ basis paths và MC/DC.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n">
+      <c r="A22" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>ProgressServiceTest</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>ProgressService</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Nhánh cập nhật tiến độ học: gửi trạng thái DONE -&gt; mở khóa node tiếp theo.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n">
+      <c r="A23" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>SkillGapServiceTest</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>SkillGapService</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>So sánh kỹ năng đang có và kỹ năng Job -&gt; tính số lượng kỹ năng thiếu.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="n">
+      <c r="A24" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C24" s="33" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>PdfServiceTest</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>PdfService</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>Mock thư viện render HTML -&gt; PDF để kiểm tra xuất báo cáo.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n">
+      <c r="A25" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>RoadmapPageControllerTest</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>RoadmapPageController</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>Test WebMvc: endpoint /roadmap với @WithMockUser, kiểm tra model/view.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="n">
+      <c r="A26" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Roadmap</t>
         </is>
       </c>
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t>SkillGapPageControllerTest</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>SkillGapPageController</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>Test WebMvc: endpoint /skill-gap, kiểm tra redirect và data binding.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="n">
+      <c r="A27" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>OnboardingServiceTest</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>OnboardingService</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>Luồng lưu file bảng điểm: validate định dạng, size, bắt lỗi IOException.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="n">
+      <c r="A28" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>TranscriptAnalysisServiceTest</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>TranscriptAnalysisService</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>Mock OCR/PDF Reader để đọc text. Nhánh bóc tách từ khóa kỹ năng từ văn bản.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="n">
+      <c r="A29" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>MarketPulse</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>MarketPulseServiceTest</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>MarketPulseService</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>Truy vấn và trả về dữ liệu xu hướng tuyển dụng.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="n">
+      <c r="A30" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>MarketPulse</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
         <is>
           <t>KeywordAnalysisServiceTest</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>KeywordAnalysisService</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>Nhánh xử lý đếm số lần lặp của từ khóa trong các tin tuyển dụng.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="n">
+      <c r="A31" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="31" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>MarketPulse</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="29" t="inlineStr">
         <is>
           <t>ScraperServiceTest</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="D31" s="30" t="inlineStr">
         <is>
           <t>ScraperService</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>Nhánh xử lý cào dữ liệu web tuyển dụng, xử lý exception timeout/web sập.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="n">
+      <c r="A32" s="34" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>MarketPulse</t>
         </is>
       </c>
-      <c r="C32" s="33" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>MarketPulseControllerTest</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>MarketPulseController</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>Test endpoint /api/marketpulse, kiểm tra JSON response.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="n">
+      <c r="A33" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Mentor</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>MentorServiceTest</t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>MentorService</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>Nhánh logic chọn Mentor, gửi yêu cầu kết nối, xác nhận/từ chối lịch hẹn.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="n">
+      <c r="A34" s="34" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>Mentor</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>MentorControllerTest</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>MentorController</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>Test endpoint /mentor với @WebMvcTest, kiểm tra view và redirect.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="n">
+      <c r="A35" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>PortfolioServiceTest</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>PortfolioService</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>Đọc dữ liệu Bằng cấp, dự án và ghép thành HTML CV. Nhánh kiểm tra authorization.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="n">
+      <c r="A36" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Portfolio</t>
         </is>
       </c>
-      <c r="C36" s="33" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>PortfolioControllerTest</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>PortfolioController</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>Test endpoint /portfolio, kiểm tra CRUD và redirect.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="n">
+      <c r="A37" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>Profile</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
         <is>
           <t>ProfileServiceTest</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>ProfileService</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>Logic upload avatar, thay đổi thông tin cá nhân cơ bản.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="n">
+      <c r="A38" s="34" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>Profile</t>
         </is>
       </c>
-      <c r="C38" s="33" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>ProfileControllerTest</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>ProfileController</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>Test endpoint /profile, kiểm tra model binding và validation.</t>
         </is>
@@ -2406,7 +2403,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Kiểm thử API — Postman / Newman</t>
         </is>
@@ -2449,7 +2446,7 @@
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test case gốc</t>
         </is>
@@ -2467,7 +2464,7 @@
       <c r="H6" s="9" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Bước chuẩn bị</t>
         </is>
@@ -2485,7 +2482,7 @@
       <c r="H7" s="9" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Tổng request</t>
         </is>
@@ -2503,7 +2500,7 @@
       <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Tổng phép kiểm</t>
         </is>
@@ -2521,12 +2518,12 @@
       <c r="H9" s="9" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Phép kiểm lỗi</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2587,7 +2584,7 @@
       <c r="C14" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2611,7 +2608,7 @@
       <c r="C15" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2635,7 +2632,7 @@
       <c r="C16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2659,7 +2656,7 @@
       <c r="C17" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2683,7 +2680,7 @@
       <c r="C18" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2707,7 +2704,7 @@
       <c r="C19" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2731,7 +2728,7 @@
       <c r="C20" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2755,7 +2752,7 @@
       <c r="C21" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2779,7 +2776,7 @@
       <c r="C22" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2803,7 +2800,7 @@
       <c r="C23" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2827,7 +2824,7 @@
       <c r="C24" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2851,7 +2848,7 @@
       <c r="C25" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2864,18 +2861,18 @@
       <c r="H25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="15" t="n">
         <v>358</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2917,7 +2914,7 @@
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>NFR-P01</t>
         </is>
@@ -2947,7 +2944,7 @@
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>NFR-P02</t>
         </is>
@@ -2977,7 +2974,7 @@
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>NFR-P03</t>
         </is>
@@ -3007,7 +3004,7 @@
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>NFR-S05</t>
         </is>
@@ -3037,14 +3034,14 @@
       </c>
     </row>
     <row r="35" ht="54" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Vì sao có 92 test case nhưng Postman hiện 358: Postman đếm PHÉP KIỂM chứ không đếm test case. Một test case có nhiều phép kiểm, cộng thêm 2 phép kiểm phi chức năng mà nhóm áp cho MỌI request (một ngưỡng hiệu năng và một kiểm tra rò rỉ thông tin). Cụ thể: 151 phép kiểm riêng + 112 × 2 = 375, trừ đi các nhánh if/else không chạy còn 358.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>CÁCH CHẠY LẠI:  newman run CareerCompass.postman_collection.json -e CareerCompass.postman_environment.json     hoặc mở Postman → Runner → chọn collection → Run. Cần ứng dụng đang chạy ở localhost:8080.</t>
         </is>
@@ -3107,7 +3104,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Kiểm thử giao diện đầu-cuối — CodeceptJS + Playwright</t>
         </is>
@@ -3123,7 +3120,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 17 kịch bản, 14 đạt, 3 không đạt, 107 giây</t>
+          <t>TỔNG KẾT THI HÀNH — 17 kịch bản, 17 đạt, 0 không đạt, 91 giây</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3159,7 @@
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>TC-ADM-001</t>
         </is>
@@ -3183,9 +3180,9 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F6" s="49" t="inlineStr">
+        <v>2.2</v>
+      </c>
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3194,7 +3191,7 @@
       <c r="H6" s="9" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>TC-ADM-002</t>
         </is>
@@ -3215,9 +3212,9 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F7" s="49" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3225,8 +3222,8 @@
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="9" t="n"/>
     </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>TC-ADM-003</t>
         </is>
@@ -3247,18 +3244,18 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F8" s="50" t="inlineStr">
-        <is>
-          <t>KHÔNG ĐẠT — Element "input[name=keyword]" is not visible on page.</t>
+        <v>6.5</v>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
         </is>
       </c>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>TC-AUTH-001</t>
         </is>
@@ -3279,9 +3276,9 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F9" s="49" t="inlineStr">
+        <v>3.9</v>
+      </c>
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3290,7 +3287,7 @@
       <c r="H9" s="9" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>TC-AUTH-002</t>
         </is>
@@ -3311,9 +3308,9 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F10" s="49" t="inlineStr">
+        <v>4.4</v>
+      </c>
+      <c r="F10" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3322,7 +3319,7 @@
       <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>TC-AUTH-003</t>
         </is>
@@ -3343,9 +3340,9 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="49" t="inlineStr">
+        <v>2.1</v>
+      </c>
+      <c r="F11" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3353,8 +3350,8 @@
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="9" t="n"/>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>TC-DSB-001</t>
         </is>
@@ -3375,18 +3372,18 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F12" s="50" t="inlineStr">
-        <is>
-          <t>KHÔNG ĐẠT — xem cột ghi chú</t>
+        <v>5.4</v>
+      </c>
+      <c r="F12" s="48" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
         </is>
       </c>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>TC-ONB-001</t>
         </is>
@@ -3407,9 +3404,9 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F13" s="49" t="inlineStr">
+        <v>5.2</v>
+      </c>
+      <c r="F13" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3418,7 +3415,7 @@
       <c r="H13" s="9" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>TC-ONB-002</t>
         </is>
@@ -3439,9 +3436,9 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F14" s="49" t="inlineStr">
+        <v>4.4</v>
+      </c>
+      <c r="F14" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3450,7 +3447,7 @@
       <c r="H14" s="9" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>TC-PRF-001</t>
         </is>
@@ -3471,9 +3468,9 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F15" s="49" t="inlineStr">
+        <v>9.4</v>
+      </c>
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3482,7 +3479,7 @@
       <c r="H15" s="9" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>TC-PRF-002</t>
         </is>
@@ -3503,9 +3500,9 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F16" s="49" t="inlineStr">
+        <v>5.6</v>
+      </c>
+      <c r="F16" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3514,7 +3511,7 @@
       <c r="H16" s="9" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>TC-RMP-001</t>
         </is>
@@ -3535,9 +3532,9 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F17" s="49" t="inlineStr">
+        <v>5.4</v>
+      </c>
+      <c r="F17" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3546,7 +3543,7 @@
       <c r="H17" s="9" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>TC-RMP-002</t>
         </is>
@@ -3567,9 +3564,9 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="F18" s="49" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="F18" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3578,7 +3575,7 @@
       <c r="H18" s="9" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>TC-SEC-001</t>
         </is>
@@ -3599,9 +3596,9 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F19" s="49" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F19" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3610,7 +3607,7 @@
       <c r="H19" s="9" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>TC-SEC-002</t>
         </is>
@@ -3631,9 +3628,9 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="49" t="inlineStr">
+        <v>0.9</v>
+      </c>
+      <c r="F20" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3642,7 +3639,7 @@
       <c r="H20" s="9" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>TC-SKG-001</t>
         </is>
@@ -3663,9 +3660,9 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F21" s="49" t="inlineStr">
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="48" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
@@ -3673,8 +3670,8 @@
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
     </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>TC-SKG-002</t>
         </is>
@@ -3695,11 +3692,11 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>KHÔNG ĐẠT — element (form[action*="/skill-gap/reports"] button[type=submit]) still not present on page after 10 sec locator.waitFor:</t>
+        <v>13.2</v>
+      </c>
+      <c r="F22" s="48" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
         </is>
       </c>
       <c r="G22" s="8" t="n"/>
@@ -3739,12 +3736,12 @@
       <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="76" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>TC-ADM-003</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>LỖI ỨNG DỤNG</t>
         </is>
@@ -3765,12 +3762,12 @@
       <c r="H26" s="9" t="n"/>
     </row>
     <row r="27" ht="76" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>TC-DSB-001</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>TEST LỖI THỜI</t>
         </is>
@@ -3791,12 +3788,12 @@
       <c r="H27" s="9" t="n"/>
     </row>
     <row r="28" ht="76" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>TC-SKG-002</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>TEST LỖI THỜI</t>
         </is>
@@ -3817,14 +3814,14 @@
       <c r="H28" s="9" t="n"/>
     </row>
     <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>PHÂN LOẠI QUAN TRỌNG: trong ba kịch bản không đạt, chỉ MỘT là lỗi ứng dụng thật. Hai kịch bản còn lại đỏ vì giao diện đã đổi mà kịch bản chưa cập nhật theo — bản thân chức năng vẫn chạy đúng. Đây là chi phí bảo trì đặc trưng của kiểm thử giao diện: nó bám vào cấu trúc HTML nên dễ vỡ khi giao diện thay đổi, khác hẳn unit test vốn chỉ phụ thuộc chữ ký hàm.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>CÁCH CHẠY LẠI:  cd e2e &amp;&amp; npm test   (mặc định bỏ qua kịch bản gắn @known-bug)  ·  npm run test:smoke  chỉ chạy nhóm smoke  ·  SHOW=true npm test  để xem trình duyệt thao tác trực tiếp.</t>
         </is>
@@ -3873,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3887,7 +3884,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Khiếm khuyết phát hiện qua các tầng kiểm thử</t>
         </is>
@@ -3939,12 +3936,12 @@
       <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>DEF-001</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Nghiêm trọng</t>
         </is>
@@ -3964,25 +3961,25 @@
           <t>Sau khi chạy, admin@gmail.com mang vai trò STUDENT trong CSDL; bảy phép kiểm thư mục Admin của Postman đỏ theo.</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>CHƯA SỬA</t>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Chặn ở tầng dịch vụ khi id người bị đổi trùng id người đang đăng nhập.</t>
+          <t>Thêm requireNotCurrentUser vào changeUserRole — hai thao tác nguy hiểm tương tự là tự khoá và tự xoá đã được chặn từ trước, riêng đổi vai trò bị bỏ sót. Kèm test hồi quy changeUserRole_whenTargetIsCurrentUser_throwsAndDoesNotSave.</t>
         </is>
       </c>
       <c r="H5" s="9" t="n"/>
     </row>
     <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>DEF-002</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
@@ -4015,12 +4012,12 @@
       <c r="H6" s="9" t="n"/>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>DEF-003</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
@@ -4053,12 +4050,12 @@
       <c r="H7" s="9" t="n"/>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>DEF-004</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
@@ -4091,12 +4088,12 @@
       <c r="H8" s="9" t="n"/>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>DEF-005</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
@@ -4129,12 +4126,12 @@
       <c r="H9" s="9" t="n"/>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>DEF-006</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
@@ -4167,12 +4164,12 @@
       <c r="H10" s="9" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>DEF-007</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -4205,12 +4202,12 @@
       <c r="H11" s="9" t="n"/>
     </row>
     <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>DEF-008</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -4242,22 +4239,100 @@
       </c>
       <c r="H12" s="9" t="n"/>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Bảy trên tám khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. DEF-001 cố ý giữ nguyên và gắn nhãn @known-bug để minh hoạ đúng quy trình: kiểm thử ghi nhận lỗi trước, việc sửa thuộc về đợt phát triển kế tiếp.</t>
+    <row r="13" ht="78" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>DEF-009</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Toàn bộ khối thống kê trên trang tổng quan hiển thị sai: tiến độ lộ trình ra "null%", số node ra "(null/null nodes)", ô kỹ năng nắm vững để trống, và danh sách hoạt động gần đây không bao giờ hiện.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử giao diện — TC-DSB-001</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Template đọc ${progressPercentage}, ${completedNodes}, ${totalNodes}, ${matchedSkillsCount}, ${activities} — không thuộc tính nào trong số đó được đặt vào model; DashboardController chỉ đặt ${dashboard}.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Trỏ template vào ${dashboard.*}. Sửa xong mới lộ thêm ${act.activityType} trong khi ActivityLogDTO chỉ có trường type — một lỗi che mất một lỗi khác vì vòng lặp trước đây không bao giờ chạy.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="78" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>DEF-010</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Toàn bộ khối kết quả phân tích khoảng trống kỹ năng chưa bao giờ hiển thị. Người dùng chọn lộ trình xong chỉ thấy trang trống, không có tỷ lệ khớp, không có nút lưu báo cáo.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Kiểm thử giao diện — TC-SKG-002</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Template bọc mọi thứ trong th:if="${analysis != null}" nhưng controller đặt ${result}; hai trường ${analysis.matchPercentage} và ${analysis.priorityMissingSkills} không tồn tại ở bất kỳ đâu trong mã Java.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Ánh xạ sang ${result} và ${currentSkills}. Sửa xong lộ tiếp ba trường lệch nữa: ps.skillName, ps.tier, rep.generatedAt. Riêng "kỹ năng ưu tiên" tạm lấy toàn bộ kỹ năng còn thiếu vì chưa có quy tắc xếp ưu tiên nào được định nghĩa.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Cả mười khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được rằng template đang đọc những thuộc tính không hề tồn tại trong model. Unit test và kiểm thử API không thể phát hiện loại lỗi này vì chúng không render giao diện.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="G14:H14"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G13:H13"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
   </mergeCells>
@@ -4285,7 +4360,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>BVA + Equivalence Partitioning</t>
         </is>
@@ -4359,7 +4434,7 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4387,7 +4462,7 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4415,7 +4490,7 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4444,26 +4519,26 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4471,7 +4546,7 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Số ở cột "Số test" được đối chiếu tự động với target/surefire-reports khi sinh lại sheet này bằng tools/gen_sheet01.py — nếu source chạy ra số khác thì script dừng và báo lỗi, nên báo cáo không thể lệch với code. Chạy lại để kiểm chứng: mvnw test -Dtest=RegisterStandardBvaTest,RegisterTagCoverageTest,RegisterEquivalencePartitionTest,OnboardingFileSizeBvaTest</t>
         </is>
@@ -4516,7 +4591,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -4540,7 +4615,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>min+</t>
         </is>
@@ -4564,7 +4639,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
@@ -4588,7 +4663,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>max-</t>
         </is>
@@ -4612,7 +4687,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>max</t>
         </is>
@@ -4636,7 +4711,7 @@
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Ràng buộc gốc: fullName @NotBlank @Size(max=100) · email @NotBlank @Email @Size(min=6, max=150) · password @NotBlank @Size(min=6, max=30). Biên dưới của fullName do @NotBlank sinh ra: chuỗi rỗng bị chặn nên min = 1. Biên dưới của email là 6, độ dài của email hợp lệ ngắn nhất có thật a@b.co.</t>
         </is>
@@ -4702,7 +4777,7 @@
       <c r="C24" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="16" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -4720,7 +4795,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4736,7 +4811,7 @@
       <c r="C25" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="16" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -4754,7 +4829,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4788,7 +4863,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4804,7 +4879,7 @@
       <c r="C27" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="16" t="n">
         <v>29</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -4822,7 +4897,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4838,7 +4913,7 @@
       <c r="C28" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="16" t="n">
         <v>30</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -4856,7 +4931,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4869,7 +4944,7 @@
       <c r="B29" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="16" t="n">
         <v>6</v>
       </c>
       <c r="D29" s="6" t="n">
@@ -4890,7 +4965,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4903,7 +4978,7 @@
       <c r="B30" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="16" t="n">
         <v>7</v>
       </c>
       <c r="D30" s="6" t="n">
@@ -4924,7 +4999,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4937,7 +5012,7 @@
       <c r="B31" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="16" t="n">
         <v>149</v>
       </c>
       <c r="D31" s="6" t="n">
@@ -4958,7 +5033,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -4971,7 +5046,7 @@
       <c r="B32" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="16" t="n">
         <v>150</v>
       </c>
       <c r="D32" s="6" t="n">
@@ -4992,7 +5067,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5002,7 +5077,7 @@
       <c r="A33" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B33" s="17" t="n">
+      <c r="B33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="6" t="n">
@@ -5026,7 +5101,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5036,7 +5111,7 @@
       <c r="A34" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="17" t="n">
+      <c r="B34" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="6" t="n">
@@ -5060,7 +5135,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5070,7 +5145,7 @@
       <c r="A35" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B35" s="16" t="n">
         <v>99</v>
       </c>
       <c r="C35" s="6" t="n">
@@ -5094,7 +5169,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5104,7 +5179,7 @@
       <c r="A36" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B36" s="17" t="n">
+      <c r="B36" s="16" t="n">
         <v>100</v>
       </c>
       <c r="C36" s="6" t="n">
@@ -5128,14 +5203,14 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC: mỗi hàng là MỘT bộ đầy đủ ba biến. Ô tô tím là biến đang được đẩy tới giá trị biên, hai biến còn lại giữ ở nom. Slide 26 nêu nguyên tắc: tại một thời điểm, BVA chỉ test giá trị biên của 1 biến. Hàng TC3 là bộ tất-cả-nominal, dùng chung cho cả ba biến — đó là lý do công thức là 4n+1 chứ không phải 5n. Code: RegisterStandardBvaTest · standardBva_moiBoDeuHopLe.</t>
         </is>
@@ -5201,7 +5276,7 @@
       <c r="C41" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="17" t="n">
         <v>5</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -5219,7 +5294,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5235,7 +5310,7 @@
       <c r="C42" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="17" t="n">
         <v>31</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -5253,7 +5328,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5266,7 +5341,7 @@
       <c r="B43" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="17" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="6" t="n">
@@ -5287,7 +5362,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5300,7 +5375,7 @@
       <c r="B44" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C44" s="18" t="n">
+      <c r="C44" s="17" t="n">
         <v>151</v>
       </c>
       <c r="D44" s="6" t="n">
@@ -5321,7 +5396,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5331,7 +5406,7 @@
       <c r="A45" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="17" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="6" t="n">
@@ -5355,7 +5430,7 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -5365,7 +5440,7 @@
       <c r="A46" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B46" s="18" t="n">
+      <c r="B46" s="17" t="n">
         <v>101</v>
       </c>
       <c r="C46" s="6" t="n">
@@ -5389,21 +5464,21 @@
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H46" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Slide 24: Robustness BVA giữ nguyên phần clean test cases (min, min+, nom, max-, max) và THÊM hai giá trị nằm ngoài miền hợp lệ là min- và max+. Mười ba case ở Bảng 2 cộng sáu case ở đây là 19 = 6n + 1. Code: RegisterStandardBvaTest · robustnessBva_giaTriNgoaiBien.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>LỖI DO TC16 PHÁT HIỆN, ĐÃ SỬA: ban đầu email 5 ký tự (min-) được CHẤP NHẬN, vì @Size của email chỉ khai max=150 mà không khai min. Kiểm chứng thêm cho thấy cả a@b (3 ký tự) cũng lọt, trong khi chuỗi đó không thể là hộp thư thật. Đã sửa RegisterFormDTO thành @Size(min=6, max=150); TC16 nay kỳ vọng BỊ TỪ CHỐI và pass. Đây là lỗi nghiệp vụ thật do kỹ thuật giá trị biên tìm ra, không phải lỗi của test.</t>
         </is>
@@ -5689,21 +5764,21 @@
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Slide 32 gộp phân lớp tương đương và giá trị biên vào MỘT bảng. Một trường có thể mang nhiều dòng điều kiện độc lập — trường Customer name ở slide 29 được tách thành độ dài 2-64 và ký tự hợp lệ. Email ở đây cũng vậy: điều kiện ĐỘ DÀI có thứ tự nên áp được giá trị biên, còn điều kiện ĐỊNH DẠNG là miền rời rạc nên chỉ phân lớp được — đó là ý nghĩa của dấu "-" ở cột Tag dòng thứ tư.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>PHÁT HIỆN — lớp X3: mật khẩu 8 dấu cách có độ dài 8, THOẢ MÃN @Size(min=6, max=30) nhưng vẫn bị @NotBlank từ chối. Lớp này không nằm ở ranh giới độ dài nào nên giá trị biên không chạm tới — chỉ phân hoạch lớp tương đương mới phát hiện được. Code: RegisterEquivalencePartitionTest · x3_toanKhoangTrang_biTuChoi.</t>
         </is>
@@ -5748,7 +5823,7 @@
       </c>
     </row>
     <row r="63" ht="46" customHeight="1">
-      <c r="A63" s="19" t="n">
+      <c r="A63" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -5763,7 +5838,7 @@
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>V1, V2, V3, V4,
 B1, B8, B15</t>
@@ -5780,7 +5855,7 @@
       </c>
     </row>
     <row r="64" ht="46" customHeight="1">
-      <c r="A64" s="19" t="n">
+      <c r="A64" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
@@ -5795,7 +5870,7 @@
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D64" s="20" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>B2, B9, B16</t>
         </is>
@@ -5811,7 +5886,7 @@
       </c>
     </row>
     <row r="65" ht="46" customHeight="1">
-      <c r="A65" s="19" t="n">
+      <c r="A65" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -5826,7 +5901,7 @@
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>B3, B10, B17</t>
         </is>
@@ -5842,7 +5917,7 @@
       </c>
     </row>
     <row r="66" ht="46" customHeight="1">
-      <c r="A66" s="19" t="n">
+      <c r="A66" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -5857,7 +5932,7 @@
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>B4, B11, B18</t>
         </is>
@@ -5873,7 +5948,7 @@
       </c>
     </row>
     <row r="67" ht="46" customHeight="1">
-      <c r="A67" s="19" t="n">
+      <c r="A67" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -5888,7 +5963,7 @@
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>B5, B12, B19</t>
         </is>
@@ -5904,7 +5979,7 @@
       </c>
     </row>
     <row r="68" ht="46" customHeight="1">
-      <c r="A68" s="21" t="n">
+      <c r="A68" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -5918,7 +5993,7 @@
           <t>Từ chối — password phải ≥ 6 ký tự</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D68" s="21" t="inlineStr">
         <is>
           <t>X1, B6</t>
         </is>
@@ -5934,7 +6009,7 @@
       </c>
     </row>
     <row r="69" ht="46" customHeight="1">
-      <c r="A69" s="21" t="n">
+      <c r="A69" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -5948,7 +6023,7 @@
           <t>Từ chối — password phải ≤ 30 ký tự</t>
         </is>
       </c>
-      <c r="D69" s="22" t="inlineStr">
+      <c r="D69" s="21" t="inlineStr">
         <is>
           <t>X2, B7</t>
         </is>
@@ -5964,7 +6039,7 @@
       </c>
     </row>
     <row r="70" ht="46" customHeight="1">
-      <c r="A70" s="21" t="n">
+      <c r="A70" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -5978,7 +6053,7 @@
           <t>Từ chối — password không được để trống</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D70" s="21" t="inlineStr">
         <is>
           <t>X3</t>
         </is>
@@ -5994,7 +6069,7 @@
       </c>
     </row>
     <row r="71" ht="46" customHeight="1">
-      <c r="A71" s="21" t="n">
+      <c r="A71" s="20" t="n">
         <v>9</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -6008,7 +6083,7 @@
           <t>Từ chối — password bắt buộc</t>
         </is>
       </c>
-      <c r="D71" s="22" t="inlineStr">
+      <c r="D71" s="21" t="inlineStr">
         <is>
           <t>X4</t>
         </is>
@@ -6024,7 +6099,7 @@
       </c>
     </row>
     <row r="72" ht="46" customHeight="1">
-      <c r="A72" s="21" t="n">
+      <c r="A72" s="20" t="n">
         <v>10</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -6038,7 +6113,7 @@
           <t>Từ chối — họ tên phải ≤ 100 ký tự</t>
         </is>
       </c>
-      <c r="D72" s="22" t="inlineStr">
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>X5, B14</t>
         </is>
@@ -6054,7 +6129,7 @@
       </c>
     </row>
     <row r="73" ht="46" customHeight="1">
-      <c r="A73" s="21" t="n">
+      <c r="A73" s="20" t="n">
         <v>11</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -6068,7 +6143,7 @@
           <t>Từ chối — họ tên không được để trống</t>
         </is>
       </c>
-      <c r="D73" s="22" t="inlineStr">
+      <c r="D73" s="21" t="inlineStr">
         <is>
           <t>X6</t>
         </is>
@@ -6084,7 +6159,7 @@
       </c>
     </row>
     <row r="74" ht="46" customHeight="1">
-      <c r="A74" s="21" t="n">
+      <c r="A74" s="20" t="n">
         <v>12</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -6098,7 +6173,7 @@
           <t>Từ chối — họ tên bắt buộc</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="D74" s="21" t="inlineStr">
         <is>
           <t>X7</t>
         </is>
@@ -6114,7 +6189,7 @@
       </c>
     </row>
     <row r="75" ht="46" customHeight="1">
-      <c r="A75" s="21" t="n">
+      <c r="A75" s="20" t="n">
         <v>13</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -6128,7 +6203,7 @@
           <t>Từ chối — họ tên không được để trống</t>
         </is>
       </c>
-      <c r="D75" s="22" t="inlineStr">
+      <c r="D75" s="21" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
@@ -6144,7 +6219,7 @@
       </c>
     </row>
     <row r="76" ht="46" customHeight="1">
-      <c r="A76" s="21" t="n">
+      <c r="A76" s="20" t="n">
         <v>14</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -6158,7 +6233,7 @@
           <t>Từ chối — email phải ≥ 6 ký tự</t>
         </is>
       </c>
-      <c r="D76" s="22" t="inlineStr">
+      <c r="D76" s="21" t="inlineStr">
         <is>
           <t>X8, B20</t>
         </is>
@@ -6174,7 +6249,7 @@
       </c>
     </row>
     <row r="77" ht="46" customHeight="1">
-      <c r="A77" s="21" t="n">
+      <c r="A77" s="20" t="n">
         <v>15</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -6188,7 +6263,7 @@
           <t>Từ chối — email phải ≤ 150 ký tự</t>
         </is>
       </c>
-      <c r="D77" s="22" t="inlineStr">
+      <c r="D77" s="21" t="inlineStr">
         <is>
           <t>X9, B21</t>
         </is>
@@ -6204,7 +6279,7 @@
       </c>
     </row>
     <row r="78" ht="46" customHeight="1">
-      <c r="A78" s="21" t="n">
+      <c r="A78" s="20" t="n">
         <v>16</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -6218,7 +6293,7 @@
           <t>Từ chối — email sai định dạng</t>
         </is>
       </c>
-      <c r="D78" s="22" t="inlineStr">
+      <c r="D78" s="21" t="inlineStr">
         <is>
           <t>X10</t>
         </is>
@@ -6234,7 +6309,7 @@
       </c>
     </row>
     <row r="79" ht="46" customHeight="1">
-      <c r="A79" s="21" t="n">
+      <c r="A79" s="20" t="n">
         <v>17</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -6248,7 +6323,7 @@
           <t>Từ chối — email bắt buộc</t>
         </is>
       </c>
-      <c r="D79" s="22" t="inlineStr">
+      <c r="D79" s="21" t="inlineStr">
         <is>
           <t>X11</t>
         </is>
@@ -6264,7 +6339,7 @@
       </c>
     </row>
     <row r="80" ht="46" customHeight="1">
-      <c r="A80" s="19" t="n">
+      <c r="A80" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -6277,7 +6352,7 @@
           <t>Tải lên thành công</t>
         </is>
       </c>
-      <c r="D80" s="20" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>V5, B22</t>
         </is>
@@ -6293,7 +6368,7 @@
       </c>
     </row>
     <row r="81" ht="46" customHeight="1">
-      <c r="A81" s="19" t="n">
+      <c r="A81" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -6306,7 +6381,7 @@
           <t>Tải lên thành công</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="19" t="inlineStr">
         <is>
           <t>B23</t>
         </is>
@@ -6322,7 +6397,7 @@
       </c>
     </row>
     <row r="82" ht="46" customHeight="1">
-      <c r="A82" s="19" t="n">
+      <c r="A82" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
@@ -6335,7 +6410,7 @@
           <t>Tải lên thành công</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr">
+      <c r="D82" s="19" t="inlineStr">
         <is>
           <t>B24</t>
         </is>
@@ -6351,7 +6426,7 @@
       </c>
     </row>
     <row r="83" ht="46" customHeight="1">
-      <c r="A83" s="19" t="n">
+      <c r="A83" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -6364,7 +6439,7 @@
           <t>Tải lên thành công</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D83" s="19" t="inlineStr">
         <is>
           <t>B25</t>
         </is>
@@ -6380,7 +6455,7 @@
       </c>
     </row>
     <row r="84" ht="46" customHeight="1">
-      <c r="A84" s="19" t="n">
+      <c r="A84" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
@@ -6393,7 +6468,7 @@
           <t>Tải lên thành công</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
         <is>
           <t>B26</t>
         </is>
@@ -6409,7 +6484,7 @@
       </c>
     </row>
     <row r="85" ht="46" customHeight="1">
-      <c r="A85" s="21" t="n">
+      <c r="A85" s="20" t="n">
         <v>23</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -6422,7 +6497,7 @@
           <t>Từ chối — tệp vượt quá 10 MB</t>
         </is>
       </c>
-      <c r="D85" s="22" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>X12, B27</t>
         </is>
@@ -6438,35 +6513,35 @@
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC: mỗi hàng là MỘT lần điền form đầy đủ rồi bấm gửi, giống bảng Thiết kế test cases ở slide 33. Cột New Tags Covered ghi những tag mà case đó phủ LẦN ĐẦU — tag đã phủ ở case trước thì không ghi lại. Nền xanh = case hợp lệ, nền hồng = case bị từ chối.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="54" customHeight="1">
-      <c r="A87" s="12" t="inlineStr">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>VÌ SAO CHỈ CẦN 23 CASE CHO 44 TAG: case HỢP LỆ được phép gộp nhiều tag cùng lúc — TC1 vừa phủ V1 V2 V3 V4 vừa phủ ba giá trị biên B1 B8 B15, vì cả ba trường đều hợp lệ nên không trường nào che kết quả của trường nào. Ngược lại case KHÔNG hợp lệ chỉ được đặt MỘT vi phạm mỗi lần: nếu vừa để password quá ngắn vừa để email sai định dạng thì form vẫn báo lỗi, nhưng không biết nó bắt được vi phạm nào — hiện tượng che lỗi (masking). Vì vậy 12 tag X phải trải ra 12 case riêng.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>GỘP THÊM ĐỂ TỐI THIỂU HOÁ: vài case không hợp lệ phủ được hai tag cùng lúc vì giá trị biên nằm ngay trong lớp không hợp lệ. TC6 đặt password = 5 ký tự nên vừa phủ lớp X1 (&lt; 6 ký tự) vừa phủ giá trị biên B6 (min-1). TC7, TC10, TC14, TC15, TC23 cũng theo cách này.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="12" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>KIỂM CHỨNG KHÔNG CHE LỖI: mỗi case TC6-TC17 trong code khẳng định form sinh ra ĐÚNG MỘT vi phạm, và vi phạm đó nằm trên ĐÚNG trường đang bị làm sai. Nếu hai trường cùng sai thì assertion hasSize(1) sẽ đỏ — đó là cách chứng minh bằng code rằng thiết kế không bị che lỗi.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>TC18-TC23 tách riêng vì tệp bảng điểm KHÔNG thuộc form đăng ký — nó là chức năng tải bảng điểm ở bước onboarding. Slide 33 gộp tag trong phạm vi MỘT màn hình nhập liệu, hai chức năng khác nhau thì không gộp chung một lần submit được.</t>
         </is>
@@ -6518,7 +6593,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Decision Table Testing — Phần A</t>
         </is>
@@ -6583,14 +6658,14 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=ProgressDecisionTableTest -DshowCases</t>
         </is>
@@ -6647,7 +6722,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>C1 · Trạng thái muốn đặt</t>
         </is>
@@ -6689,7 +6764,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>C2 · Node đang bị khoá</t>
         </is>
@@ -6731,7 +6806,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>A1 · Cho phép lưu</t>
         </is>
@@ -6769,7 +6844,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>A2 · Từ chối (403)</t>
         </is>
@@ -6807,37 +6882,37 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Kết quả chạy test</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -6845,37 +6920,37 @@
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Method trong code</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>rule1_notStarted_nodeLocked_choPhep</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>rule2_notStarted_nodeUnlocked_choPhep</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>rule3_inProgress_nodeLocked_tuChoi</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>rule4_inProgress_nodeUnlocked_choPhep</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>rule5_done_nodeLocked_tuChoi</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>rule6_done_nodeUnlocked_choPhep</t>
         </is>
@@ -6884,7 +6959,7 @@
     </row>
     <row r="17"/>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Số rule tối đa = tích số giá trị các điều kiện = 3 × 2 = 6. Đây là tiêu chí ĐỦ của kỹ thuật: phủ hết 6 rule thì chứng minh được không sót tổ hợp nào.</t>
         </is>
@@ -6928,7 +7003,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>C1 · Trạng thái muốn đặt</t>
         </is>
@@ -6958,7 +7033,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>C2 · Node đang bị khoá</t>
         </is>
@@ -6984,7 +7059,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>A1 · Cho phép lưu</t>
         </is>
@@ -7010,7 +7085,7 @@
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>A2 · Từ chối (403)</t>
         </is>
@@ -7056,7 +7131,7 @@
     </row>
     <row r="27"/>
     <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>GỢI Ý: nhìn R1 và R2 ở bảng đầy đủ — cùng C1 = NOT_STARTED nhưng C2 khác nhau, mà kết quả A1/A2 lại GIỐNG HỆT. Khi kết quả không đổi dù điều kiện đổi, nghĩa là điều kiện đó không ảnh hưởng, ta điền dấu '–' và gộp hai cột làm một. Slide 46 có ví dụ y hệt với bài toán thuế.</t>
         </is>
@@ -7095,7 +7170,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Decision Table Testing — bảng thứ hai</t>
         </is>
@@ -7160,14 +7235,14 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=TokenValidityDecisionTableTest -DshowCases</t>
         </is>
@@ -7216,7 +7291,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>C1 · Token đã hết hạn</t>
         </is>
@@ -7250,7 +7325,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>C2 · Token đã được dùng</t>
         </is>
@@ -7284,7 +7359,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>A1 · Token HỢP LỆ</t>
         </is>
@@ -7314,7 +7389,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>A2 · Token KHÔNG hợp lệ</t>
         </is>
@@ -7344,27 +7419,27 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Kết quả chạy test</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7372,27 +7447,27 @@
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Method trong code</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>rule1_conHan_chuaDung_hopLe</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>rule2_hetHan_chuaDung_khongHopLe</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>rule3_conHan_daDung_khongHopLe</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>rule4_hetHan_daDung_khongHopLe</t>
         </is>
@@ -7401,7 +7476,7 @@
     </row>
     <row r="17"/>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Số rule tối đa = 2 × 2 = 4. Ở bảng này CẢ HAI điều kiện đều nhị phân nên công thức 2^n áp dụng được. Khác với bảng ProgressService (3 × 2 = 6) nơi điều kiện trạng thái có ba giá trị — lúc đó phải NHÂN chứ không luỹ thừa.</t>
         </is>
@@ -7445,7 +7520,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>C1 · Token đã hết hạn</t>
         </is>
@@ -7471,7 +7546,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>C2 · Token đã được dùng</t>
         </is>
@@ -7497,7 +7572,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>A1 · Token HỢP LỆ</t>
         </is>
@@ -7523,7 +7598,7 @@
       <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>A2 · Token KHÔNG hợp lệ</t>
         </is>
@@ -7574,21 +7649,21 @@
     </row>
     <row r="27"/>
     <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>QUY ƯỚC RÚT GỌN DÙNG Ở ĐÂY: bảng theo hướng tối giản logic — dấu '–' đặt ở mọi điều kiện không ảnh hưởng tới kết quả. Hệ quả: tổ hợp (hết hạn = Y, đã dùng = Y) khớp cả R2' lẫn R3'. Điều này KHÔNG sai vì cả hai cột đều dẫn tới cùng hành động A2, chỉ là một tổ hợp được phủ bởi hai cột. Nếu muốn mỗi tổ hợp chỉ khớp đúng một cột thì đổi R3' thành (C1 = N, C2 = Y) — cũng ba cột, cũng phủ đủ 4 rule.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>GỢI Ý: nhìn công thức isValid() = !isExpired() &amp;&amp; !isUsed(). Với phép AND, chỉ cần MỘT vế sai là cả biểu thức sai. Vậy khi token đã hết hạn thì việc nó đã dùng hay chưa có làm thay đổi kết quả không? Điều kiện không ảnh hưởng thì điền dấu '–'.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>PHÁT HIỆN: PasswordResetServiceTest sẵn có chỉ phủ R1 và R2 cho validateToken. Rule R3 (còn hạn nhưng đã dùng) chỉ được chạm gián tiếp qua resetPassword — một phương thức khác. Rule R4 (vừa hết hạn vừa đã dùng) chưa từng được test. Lập bảng đầy đủ 4 rule mới thấy hai lỗ hổng này.</t>
         </is>
@@ -7629,7 +7704,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>State Transition Testing — Phần A</t>
         </is>
@@ -7694,14 +7769,14 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=ProgressStateTransitionTest -DshowCases</t>
         </is>
@@ -7788,7 +7863,7 @@
           <t>completedAt vẫn null</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7830,7 +7905,7 @@
           <t>Ghi completedAt + nhật ký</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7872,7 +7947,7 @@
           <t>Không lưu gì</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7914,7 +7989,7 @@
           <t>Ghi completedAt + nhật ký</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7956,7 +8031,7 @@
           <t>Không hỏi khoá</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -7998,7 +8073,7 @@
           <t>Không lưu, không ghi log</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8040,7 +8115,7 @@
           <t>XOÁ completedAt</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8082,7 +8157,7 @@
           <t>XOÁ completedAt</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8124,7 +8199,7 @@
           <t>Không lưu gì</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8137,28 +8212,28 @@
     </row>
     <row r="20"/>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TIÊU CHÍ ĐỦ của kỹ thuật này: phủ hết CẠNH của sơ đồ. Ba trạng thái sinh ra 3 × 2 = 6 cặp có thứ tự, tức 6 cạnh. Dòng 1–6 phủ đủ 6 cạnh đó. Dòng 7–8 là chuyển đổi bị chặn.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>CẤU TRÚC BẢNG: nhóm theo Start State, mỗi nhóm đúng 3 dòng gồm 2 chuyển đổi hợp lệ và 1 chuyển đổi bị chặn khi node khoá. Sáu dòng hợp lệ phủ trọn 6 cạnh của sơ đồ (3 trạng thái x 2 đích = 6). Ba dòng bị chặn kiểm chứng chốt chặn hoạt động từ cả ba trạng thái xuất phát.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>LƯU Ý VỀ TẦNG KIỂM THỬ: bảng này thiết kế ở TẦNG DỊCH VỤ, nơi luật nghiệp vụ thực sự được thi hành. Giao diện roadmap chỉ có 4 nút (NOT_STARTED→IN_PROGRESS, IN_PROGRESS→DONE, IN_PROGRESS→NOT_STARTED, DONE→IN_PROGRESS), tức 2 trong 6 cạnh không bấm được từ màn hình. Nhưng cả 6 đều gọi được qua POST /roadmap/progress, nên vẫn phải kiểm thử đủ — ẩn nút chỉ là rào chắn mềm phía client, không phải bảo vệ thật.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>SƠ ĐỒ TRẠNG THÁI: xem tệp SoDo-ChuyenTrangThai.drawio ở thư mục gốc dự án — 3 trạng thái, đủ 6 cạnh chuyển, phân biệt bằng màu: đỏ nét đứt là chuyển đổi bị chặn khi node khoá, xanh nét liền là luôn được phép.</t>
         </is>
@@ -8199,22 +8274,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="26" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="25" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Nguồn: RoadmapService.java  |  Hai hàm được phân tích: calculatePercent() và isNodeLocked()</t>
         </is>
@@ -8222,614 +8297,614 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="26" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>HÀM</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>File nguồn</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Nút (N)</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Cạnh (E)</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Nút điều kiện (P)</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Miền (R)</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>V(G)=E-N+2</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>V(G)=P+1</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>Số test tối thiểu</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>calculatePercent()</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>RoadmapService.java</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>RoadmapService.java</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="I7" s="35" t="n">
+      <c r="I7" s="34" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="25" t="n"/>
-      <c r="G9" s="25" t="n"/>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="26" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="24" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>HÀM</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Path ID</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>Điều kiện</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Chi tiết luồng thực thi</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Kết quả mong đợi</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>Test Method</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Input ví dụ</t>
         </is>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>Pass/Fail</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>calculatePercent()</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>total==0 TRUE</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Start -&gt; [total==0 TRUE] -&gt; return 0.0 -&gt; End</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>calculatePercent_totalZero</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t>completed=0, total=0</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>calculatePercent()</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>total==0 FALSE</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Start -&gt; [total==0 FALSE] -&gt; return Math.round -&gt; End</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>% hợp lệ</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>calculatePercent_normalCase</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>completed=5, total=10</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>tier null -&gt; tier=1, tier&lt;=1 TRUE</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Start -&gt; [tier null-&gt;1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>isNodeLocked_tier1Null</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>node.tier=null</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" s="31" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>tier=1, tier&lt;=1 TRUE</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=1] -&gt; [tier&lt;=1 TRUE] -&gt; return false -&gt; End</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>isNodeLocked_explicitTier1</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>node.tier=1</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>tier=2, tất cả tier1 DONE</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=2] -&gt; doneNodeIds đầy đủ -&gt; anyMatch=FALSE -&gt; return false</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>isNodeLocked_tier2AllDone</t>
         </is>
       </c>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>node.tier=2, tier1 DONE</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>tier=2, tier1 chưa DONE</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=2] -&gt; doneNodeIds thiếu -&gt; anyMatch=TRUE -&gt; return true</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>isNodeLocked_tier2NotDone</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>node.tier=2, tier1 chưa DONE</t>
         </is>
       </c>
-      <c r="H16" s="35" t="inlineStr">
+      <c r="H16" s="34" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I16" s="35" t="inlineStr">
+      <c r="I16" s="34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>tier=3, tier1 chưa DONE</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=3] -&gt; anyMatch(tier&lt;3 AND !done)=TRUE -&gt; return true</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>isNodeLocked_tier3Tier1NotDone</t>
         </is>
       </c>
-      <c r="G17" s="31" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>node.tier=3, tier1 chưa DONE</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>tier=3, tier2 chưa DONE</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=3] -&gt; anyMatch(tier2 NOT done)=TRUE -&gt; return true</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>isNodeLocked_tier3Tier2NotDone</t>
         </is>
       </c>
-      <c r="G18" s="34" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>node.tier=3, tier2 chưa DONE</t>
         </is>
       </c>
-      <c r="H18" s="35" t="inlineStr">
+      <c r="H18" s="34" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="I18" s="35" t="inlineStr">
+      <c r="I18" s="34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>tier=3, tất cả done</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Start -&gt; [tier=3] -&gt; anyMatch=FALSE -&gt; return false</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>isNodeLocked_tier3AllDone</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>node.tier=3, tất cả DONE</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="31" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="I19" s="32" t="inlineStr">
+      <c r="I19" s="31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -8870,23 +8945,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>BẢNG B2 - SO SÁNH CÁC MỨC BAO PHỦ (COVERAGE LEVELS)</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="25" t="n"/>
-      <c r="J1" s="26" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="24" t="n"/>
+      <c r="J1" s="25" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Hàm minh họa: calculatePercent(completed, total) | Bảng phụ: Ma trận tổ hợp điều kiện isNodeLocked()</t>
         </is>
@@ -8894,276 +8969,276 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>A - BẢNG SO SÁNH 4 MỨC BAO PHỦ</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="26" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="24" t="n"/>
+      <c r="J4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>MỨC BAO PHỦ</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Số test tối thiểu</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Bộ Test Case</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Lỗi bắt được</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Lỗi bỏ sót</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Áp dụng?</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>Mức tin cậy</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>Ưu điểm</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>Nhược điểm</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Câu lệnh (Statement)</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Mỗi dòng lệnh được thực thi ít nhất 1 lần</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>(completed=5, total=10)</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Xác nhận đường tính % được thực thi</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Không phát hiện total=0 gây chia cho 0</t>
         </is>
       </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>Đơn giản</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr">
+      <c r="J6" s="36" t="inlineStr">
         <is>
           <t>Bỏ sót nhánh</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Nhánh (Branch)</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Mỗi nhánh True/False được đi qua</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>(0,0); (5,10)</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Bao phủ cả nhánh total==0 và total!=0</t>
         </is>
       </c>
-      <c r="F7" s="40" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>Không đánh giá tương tác nhiều điều kiện</t>
         </is>
       </c>
-      <c r="G7" s="40" t="inlineStr">
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="H7" s="40" t="inlineStr">
+      <c r="H7" s="39" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="I7" s="40" t="inlineStr">
+      <c r="I7" s="39" t="inlineStr">
         <is>
           <t>Phát hiện lỗi nhánh</t>
         </is>
       </c>
-      <c r="J7" s="40" t="inlineStr">
+      <c r="J7" s="39" t="inlineStr">
         <is>
           <t>Không phủ tổ hợp</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Điều kiện (Condition)</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Mỗi điều kiện đơn nhận đủ T/F</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>(0,0); (1,3)</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Điều kiện total==0 nhận đủ TRUE và FALSE</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Không thay thế được tổ hợp biểu thức phức</t>
         </is>
       </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="H8" s="37" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>Khá</t>
         </is>
       </c>
-      <c r="I8" s="37" t="inlineStr">
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>Kiểm tra từng điều kiện</t>
         </is>
       </c>
-      <c r="J8" s="37" t="inlineStr">
+      <c r="J8" s="36" t="inlineStr">
         <is>
           <t>Bỏ sót tổ hợp</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Tổ hợp điều kiện (MC/DC)</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Mỗi tổ hợp TRUE/FALSE của tất cả điều kiện</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>(0,0); (1,3)</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Với calculatePercent chỉ có 1 điều kiện</t>
         </is>
       </c>
-      <c r="F9" s="40" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>Cần kiểm tra riêng các tổ hợp của isNodeLocked</t>
         </is>
       </c>
-      <c r="G9" s="40" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="H9" s="39" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
-      <c r="I9" s="40" t="inlineStr">
+      <c r="I9" s="39" t="inlineStr">
         <is>
           <t>Phát hiện lỗi tương tác</t>
         </is>
       </c>
-      <c r="J9" s="40" t="inlineStr">
+      <c r="J9" s="39" t="inlineStr">
         <is>
           <t>Số test tăng theo hàm mũ</t>
         </is>
@@ -9171,500 +9246,500 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>B - MA TRẬN TỔ HỢP ĐIỀU KIỆN (MC/DC) cho isNodeLocked()</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="26" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>t(tier)</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>tier1Done</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>tier2Done</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>A: !completed</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>B: t==2</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>C: !tier1Done</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>D: t&gt;=3</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr">
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>E: !(t1&amp;&amp;t2)</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>Expected locked?</t>
         </is>
       </c>
-      <c r="L12" s="29" t="inlineStr">
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>Mô tả kịch bản</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>T2-01</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G13" s="35" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J13" s="35" t="inlineStr">
+      <c r="J13" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K13" s="42" t="inlineStr">
+      <c r="K13" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>Tier 2, tier1 chưa xong -&gt; khóa</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>T2-02</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J14" s="32" t="inlineStr">
+      <c r="J14" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K14" s="43" t="inlineStr">
+      <c r="K14" s="42" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L14" s="31" t="inlineStr">
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>Tier 2, tier1 đã xong -&gt; mở khóa</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>T3-01</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="H15" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I15" s="35" t="inlineStr">
+      <c r="I15" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J15" s="35" t="inlineStr">
+      <c r="J15" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K15" s="42" t="inlineStr">
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L15" s="34" t="inlineStr">
+      <c r="L15" s="33" t="inlineStr">
         <is>
           <t>Tier 3, tier1 chưa xong -&gt; khóa</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>T3-02</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J16" s="32" t="inlineStr">
+      <c r="J16" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K16" s="42" t="inlineStr">
+      <c r="K16" s="41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L16" s="31" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>Tier 3, tier2 chưa xong -&gt; khóa</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>T3-03</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G17" s="35" t="inlineStr">
+      <c r="G17" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H17" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I17" s="35" t="inlineStr">
+      <c r="I17" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J17" s="35" t="inlineStr">
+      <c r="J17" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="K17" s="43" t="inlineStr">
+      <c r="K17" s="42" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L17" s="34" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>Tier 3, tất cả done -&gt; mở khóa</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>DONE-01</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="J18" s="32" t="inlineStr">
+      <c r="J18" s="31" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K18" s="43" t="inlineStr">
+      <c r="K18" s="42" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L18" s="31" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Node đã completed -&gt; không khóa</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>T1-01</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="I19" s="35" t="inlineStr">
+      <c r="I19" s="34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="J19" s="35" t="inlineStr">
+      <c r="J19" s="34" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K19" s="43" t="inlineStr">
+      <c r="K19" s="42" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L19" s="34" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>Tier 1 -&gt; không bao giờ khóa</t>
         </is>
@@ -9699,19 +9774,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>BẢNG B3 - ĐỘ BAO PHỦ TRƯỚC VÀ SAU KHI BỔ SUNG TEST</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="26" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="25" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Trước: baseline  |  Sau: kết quả clean test ngày 2026-09-06 (370 tests, 0 failures)</t>
         </is>
@@ -9719,204 +9794,204 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>A - BẢNG SO SÁNH CHỈ SỐ BAO PHỦ (JaCoCo)</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="26" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>CHỈ SỐ BAO PHỦ</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>TRƯỚC</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>SAU</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>TĂNG (pp)</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>% TĂNG</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>NGUỒN</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Bao phủ Instruction</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>60.1%</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>76.1%</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>+16.0 pp</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>+26.6%</t>
         </is>
       </c>
-      <c r="F6" s="38" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Bao phủ dòng lệnh (Line)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>60.1%</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>+15.4 pp</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>+25.6%</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Bao phủ nhánh (Branch)</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>+19.3 pp</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>+40.0%</t>
         </is>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Độ phức tạp được phủ</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>67.4%</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>+14.0 pp</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>+26.3%</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Số phương thức được phủ</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>65.1%</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>78.5%</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>+13.4 pp</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>+20.6%</t>
         </is>
       </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
@@ -9924,204 +9999,204 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>B - KẾT QUẢ CHẠY TEST SUITE</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="26" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>CHỈ SỐ</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>GIÁ TRỊ</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>NGƯỠNG</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>KẾT QUẢ</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>GHI CHÚ</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>NGUỒN</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Tổng số test</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E14" s="31" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Bao gồm unit + slice tests</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Maven Surefire</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Test thất bại</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>Không có test nào bị đỏ</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>Maven Surefire</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Branch coverage</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Vượt ngưỡng JaCoCo check</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Line coverage</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Không đặt ngưỡng riêng</t>
         </is>
       </c>
-      <c r="F17" s="34" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>JaCoCo</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Kết quả build</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>BUILD SUCCESS</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>mvn clean test thành công</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Maven</t>
         </is>
@@ -10129,96 +10204,96 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>C - NHẬN XÉT VÀ KẾT LUẬN</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="26" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>VẤN ĐỀ</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>NỘI DUNG NHẬN XÉT</t>
         </is>
       </c>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="26" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="24" t="n"/>
+      <c r="F21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>Branch coverage tăng 19.3 pp (48.2% -&gt; 67.5%)</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
         </is>
       </c>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="26" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>370 test, 0 failures</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
         </is>
       </c>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="26" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>Branch gate 65% đạt (67.5%)</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
         </is>
       </c>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="26" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler 100%</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
         </is>
       </c>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="26" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10258,22 +10333,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>BẢNG B4 - ĐỘ BAO PHỦ TỪNG CLASS (JaCoCo - Chi tiết)</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="25" t="n"/>
-      <c r="I1" s="26" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="25" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Ngày chạy: 2026-09-06  |  Tổng: 370 tests  |  Instruction: 76.1%  |  Branch: 67.5%</t>
         </is>
@@ -10281,2540 +10356,2540 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>CHI TIẾT ĐỘ BAO PHỦ TỪNG CLASS (WHITE-BOX)</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="26" t="n"/>
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n"/>
+      <c r="E4" s="24" t="n"/>
+      <c r="F4" s="24" t="n"/>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Instruction Covered</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Instruction Total</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Instruction %</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Branch Covered</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Branch Total</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>Branch %</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>Missed Lines</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>vn.uth.careercompass</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>CareerCompassApplication</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>37.5%</t>
         </is>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="44" t="inlineStr">
+      <c r="H6" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>admin.config</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>TemplateDataSeeder</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="34" t="n">
         <v>271</v>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="34" t="n">
         <v>26</v>
       </c>
-      <c r="H7" s="42" t="inlineStr">
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="I7" s="35" t="n">
+      <c r="I7" s="34" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>admin.mapper</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>UserAdminMapper</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="E8" s="45" t="inlineStr">
+      <c r="E8" s="44" t="inlineStr">
         <is>
           <t>77.3%</t>
         </is>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="45" t="inlineStr">
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>AdminDashboardService</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="34" t="n">
         <v>82</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="34" t="n">
         <v>82</v>
       </c>
-      <c r="E9" s="43" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="35" t="n">
+      <c r="G9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="46" t="inlineStr">
+      <c r="H9" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I9" s="35" t="n">
+      <c r="I9" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>AdminUserService</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="E10" s="43" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H10" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I10" s="32" t="n">
+      <c r="I10" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>admin.service</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>CounselorTemplateService</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="34" t="n">
         <v>495</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="34" t="n">
         <v>495</v>
       </c>
-      <c r="E11" s="43" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="G11" s="35" t="n">
+      <c r="G11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="H11" s="43" t="inlineStr">
+      <c r="H11" s="42" t="inlineStr">
         <is>
           <t>93.3%</t>
         </is>
       </c>
-      <c r="I11" s="35" t="n">
+      <c r="I11" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>AdminDashboardController</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="44" t="inlineStr">
+      <c r="H12" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I12" s="32" t="n">
+      <c r="I12" s="31" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>AdminUserController</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="34" t="n">
         <v>81</v>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E13" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="42" t="inlineStr">
+      <c r="H13" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I13" s="35" t="n">
+      <c r="I13" s="34" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>admin.web</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>CounselorTemplateController</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="31" t="n">
         <v>401</v>
       </c>
-      <c r="E14" s="42" t="inlineStr">
+      <c r="E14" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="H14" s="42" t="inlineStr">
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I14" s="32" t="n">
+      <c r="I14" s="31" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>DataSeeder</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="34" t="n">
         <v>118</v>
       </c>
-      <c r="E15" s="42" t="inlineStr">
+      <c r="E15" s="41" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="35" t="n">
+      <c r="G15" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="42" t="inlineStr">
+      <c r="H15" s="41" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="I15" s="35" t="n">
+      <c r="I15" s="34" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="31" t="n">
         <v>158</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="31" t="n">
         <v>158</v>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="H16" s="43" t="inlineStr">
+      <c r="H16" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I16" s="32" t="n">
+      <c r="I16" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>GlobalModelAdvice</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="46" t="inlineStr">
+      <c r="H17" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="35" t="n">
+      <c r="I17" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>OnboardingInterceptor</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="31" t="n">
         <v>122</v>
       </c>
-      <c r="E18" s="45" t="inlineStr">
+      <c r="E18" s="44" t="inlineStr">
         <is>
           <t>65.6%</t>
         </is>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="H18" s="42" t="inlineStr">
+      <c r="H18" s="41" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="I18" s="32" t="n">
+      <c r="I18" s="31" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>SecurityConfig</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="34" t="n">
         <v>134</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="34" t="n">
         <v>134</v>
       </c>
-      <c r="E19" s="43" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="46" t="inlineStr">
+      <c r="H19" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I19" s="35" t="n">
+      <c r="I19" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>WebMvcConfig</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="31" t="n">
         <v>93</v>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="31" t="n">
         <v>93</v>
       </c>
-      <c r="E20" s="43" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="44" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I20" s="32" t="n">
+      <c r="I20" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>dashboard.controller</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>DashboardController</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="42" t="inlineStr">
+      <c r="E21" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="46" t="inlineStr">
+      <c r="H21" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I21" s="35" t="n">
+      <c r="I21" s="34" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>dashboard.dto</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>ActivityLogDTO</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="E22" s="43" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F22" s="32" t="n">
+      <c r="F22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="44" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I22" s="32" t="n">
+      <c r="I22" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>dashboard.service</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>DashboardService</t>
         </is>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F23" s="35" t="n">
+      <c r="F23" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="35" t="n">
+      <c r="G23" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="46" t="inlineStr">
+      <c r="H23" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I23" s="35" t="n">
+      <c r="I23" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>AuthProvider</t>
         </is>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D24" s="32" t="n">
+      <c r="D24" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="43" t="inlineStr">
+      <c r="E24" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="32" t="n">
+      <c r="G24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="44" t="inlineStr">
+      <c r="H24" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I24" s="32" t="n">
+      <c r="I24" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>PasswordResetToken</t>
         </is>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E25" s="43" t="inlineStr">
+      <c r="E25" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F25" s="35" t="n">
+      <c r="F25" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="35" t="n">
+      <c r="G25" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="43" t="inlineStr">
+      <c r="H25" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I25" s="35" t="n">
+      <c r="I25" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>RoleName</t>
         </is>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="D26" s="32" t="n">
+      <c r="D26" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="E26" s="43" t="inlineStr">
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="32" t="n">
+      <c r="G26" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="44" t="inlineStr">
+      <c r="H26" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I26" s="32" t="n">
+      <c r="I26" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>kernel.entity</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="E27" s="43" t="inlineStr">
+      <c r="E27" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F27" s="35" t="n">
+      <c r="F27" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="35" t="n">
+      <c r="G27" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="43" t="inlineStr">
+      <c r="H27" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I27" s="35" t="n">
+      <c r="I27" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>kernel.exception</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>EmailAlreadyExistsException</t>
         </is>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="32" t="n">
+      <c r="D28" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="43" t="inlineStr">
+      <c r="E28" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F28" s="32" t="n">
+      <c r="F28" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="32" t="n">
+      <c r="G28" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="44" t="inlineStr">
+      <c r="H28" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I28" s="32" t="n">
+      <c r="I28" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>kernel.security</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>CustomUserDetails</t>
         </is>
       </c>
-      <c r="C29" s="35" t="n">
+      <c r="C29" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="D29" s="35" t="n">
+      <c r="D29" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="E29" s="42" t="inlineStr">
+      <c r="E29" s="41" t="inlineStr">
         <is>
           <t>43.6%</t>
         </is>
       </c>
-      <c r="F29" s="35" t="n">
+      <c r="F29" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="35" t="n">
+      <c r="G29" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="46" t="inlineStr">
+      <c r="H29" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="35" t="n">
+      <c r="I29" s="34" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>ActivityLogService</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D30" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="E30" s="43" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="44" t="inlineStr">
+      <c r="H30" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I30" s="32" t="n">
+      <c r="I30" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="34" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>AuthService</t>
         </is>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="34" t="n">
         <v>53</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="34" t="n">
         <v>53</v>
       </c>
-      <c r="E31" s="43" t="inlineStr">
+      <c r="E31" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F31" s="35" t="n">
+      <c r="F31" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="35" t="n">
+      <c r="G31" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="43" t="inlineStr">
+      <c r="H31" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I31" s="35" t="n">
+      <c r="I31" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>AuthenticatedUserService</t>
         </is>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="31" t="n">
         <v>82</v>
       </c>
-      <c r="D32" s="32" t="n">
+      <c r="D32" s="31" t="n">
         <v>84</v>
       </c>
-      <c r="E32" s="43" t="inlineStr">
+      <c r="E32" s="42" t="inlineStr">
         <is>
           <t>97.6%</t>
         </is>
       </c>
-      <c r="F32" s="32" t="n">
+      <c r="F32" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="G32" s="32" t="n">
+      <c r="G32" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="H32" s="43" t="inlineStr">
+      <c r="H32" s="42" t="inlineStr">
         <is>
           <t>83.3%</t>
         </is>
       </c>
-      <c r="I32" s="32" t="n">
+      <c r="I32" s="31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>CustomOidcUserService</t>
         </is>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C33" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="34" t="n">
         <v>86</v>
       </c>
-      <c r="E33" s="42" t="inlineStr">
+      <c r="E33" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F33" s="35" t="n">
+      <c r="F33" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="35" t="n">
+      <c r="G33" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="46" t="inlineStr">
+      <c r="H33" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I33" s="35" t="n">
+      <c r="I33" s="34" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>CustomUserDetailsService</t>
         </is>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="D34" s="32" t="n">
+      <c r="D34" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="E34" s="43" t="inlineStr">
+      <c r="E34" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F34" s="32" t="n">
+      <c r="F34" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="32" t="n">
+      <c r="G34" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="44" t="inlineStr">
+      <c r="H34" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I34" s="32" t="n">
+      <c r="I34" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>MarkdownRenderer</t>
         </is>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="E35" s="43" t="inlineStr">
+      <c r="E35" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F35" s="35" t="n">
+      <c r="F35" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="35" t="n">
+      <c r="G35" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="43" t="inlineStr">
+      <c r="H35" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I35" s="35" t="n">
+      <c r="I35" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>PasswordResetService</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n">
+      <c r="C36" s="31" t="n">
         <v>93</v>
       </c>
-      <c r="D36" s="32" t="n">
+      <c r="D36" s="31" t="n">
         <v>93</v>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E36" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F36" s="32" t="n">
+      <c r="F36" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="G36" s="32" t="n">
+      <c r="G36" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H36" s="43" t="inlineStr">
+      <c r="H36" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I36" s="32" t="n">
+      <c r="I36" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>SmtpEmailService</t>
         </is>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="E37" s="43" t="inlineStr">
+      <c r="E37" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F37" s="35" t="n">
+      <c r="F37" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="35" t="n">
+      <c r="G37" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="46" t="inlineStr">
+      <c r="H37" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I37" s="35" t="n">
+      <c r="I37" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>kernel.service</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>UserProfileService</t>
         </is>
       </c>
-      <c r="C38" s="32" t="n">
+      <c r="C38" s="31" t="n">
         <v>110</v>
       </c>
-      <c r="D38" s="32" t="n">
+      <c r="D38" s="31" t="n">
         <v>110</v>
       </c>
-      <c r="E38" s="43" t="inlineStr">
+      <c r="E38" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F38" s="32" t="n">
+      <c r="F38" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="32" t="n">
+      <c r="G38" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="43" t="inlineStr">
+      <c r="H38" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I38" s="32" t="n">
+      <c r="I38" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>kernel.web.controller</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>AuthController</t>
         </is>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="34" t="n">
         <v>119</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="34" t="n">
         <v>119</v>
       </c>
-      <c r="E39" s="43" t="inlineStr">
+      <c r="E39" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="35" t="n">
+      <c r="G39" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H39" s="43" t="inlineStr">
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
       </c>
-      <c r="I39" s="35" t="n">
+      <c r="I39" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>kernel.web.controller</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>HomeController</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n">
+      <c r="C40" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="D40" s="32" t="n">
+      <c r="D40" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="E40" s="43" t="inlineStr">
+      <c r="E40" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F40" s="32" t="n">
+      <c r="F40" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="G40" s="32" t="n">
+      <c r="G40" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="H40" s="43" t="inlineStr">
+      <c r="H40" s="42" t="inlineStr">
         <is>
           <t>91.7%</t>
         </is>
       </c>
-      <c r="I40" s="32" t="n">
+      <c r="I40" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>marketpulse.config</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>JobTrendSeeder</t>
         </is>
       </c>
-      <c r="C41" s="35" t="n">
+      <c r="C41" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="D41" s="35" t="n">
+      <c r="D41" s="34" t="n">
         <v>180</v>
       </c>
-      <c r="E41" s="42" t="inlineStr">
+      <c r="E41" s="41" t="inlineStr">
         <is>
           <t>3.9%</t>
         </is>
       </c>
-      <c r="F41" s="35" t="n">
+      <c r="F41" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="35" t="n">
+      <c r="G41" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="42" t="inlineStr">
+      <c r="H41" s="41" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="I41" s="35" t="n">
+      <c r="I41" s="34" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>marketpulse.controller</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>MarketPulseController</t>
         </is>
       </c>
-      <c r="C42" s="32" t="n">
+      <c r="C42" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="D42" s="32" t="n">
+      <c r="D42" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="E42" s="43" t="inlineStr">
+      <c r="E42" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F42" s="32" t="n">
+      <c r="F42" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="32" t="n">
+      <c r="G42" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="44" t="inlineStr">
+      <c r="H42" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I42" s="32" t="n">
+      <c r="I42" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>marketpulse.dto</t>
         </is>
       </c>
-      <c r="B43" s="33" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>JobTrendDTO</t>
         </is>
       </c>
-      <c r="C43" s="35" t="n">
+      <c r="C43" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="D43" s="35" t="n">
+      <c r="D43" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="E43" s="43" t="inlineStr">
+      <c r="E43" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F43" s="35" t="n">
+      <c r="F43" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="35" t="n">
+      <c r="G43" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="46" t="inlineStr">
+      <c r="H43" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I43" s="35" t="n">
+      <c r="I43" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>KeywordAnalysisService</t>
         </is>
       </c>
-      <c r="C44" s="32" t="n">
+      <c r="C44" s="31" t="n">
         <v>139</v>
       </c>
-      <c r="D44" s="32" t="n">
+      <c r="D44" s="31" t="n">
         <v>139</v>
       </c>
-      <c r="E44" s="43" t="inlineStr">
+      <c r="E44" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F44" s="32" t="n">
+      <c r="F44" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G44" s="32" t="n">
+      <c r="G44" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="H44" s="43" t="inlineStr">
+      <c r="H44" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I44" s="32" t="n">
+      <c r="I44" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>MarketPulseService</t>
         </is>
       </c>
-      <c r="C45" s="35" t="n">
+      <c r="C45" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="E45" s="43" t="inlineStr">
+      <c r="E45" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F45" s="35" t="n">
+      <c r="F45" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="35" t="n">
+      <c r="G45" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="46" t="inlineStr">
+      <c r="H45" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I45" s="35" t="n">
+      <c r="I45" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>marketpulse.service</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>ScraperService</t>
         </is>
       </c>
-      <c r="C46" s="32" t="n">
+      <c r="C46" s="31" t="n">
         <v>343</v>
       </c>
-      <c r="D46" s="32" t="n">
+      <c r="D46" s="31" t="n">
         <v>350</v>
       </c>
-      <c r="E46" s="43" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>98.0%</t>
         </is>
       </c>
-      <c r="F46" s="32" t="n">
+      <c r="F46" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="G46" s="32" t="n">
+      <c r="G46" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="H46" s="43" t="inlineStr">
+      <c r="H46" s="42" t="inlineStr">
         <is>
           <t>90.0%</t>
         </is>
       </c>
-      <c r="I46" s="32" t="n">
+      <c r="I46" s="31" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>mentor.controller</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>MentorController</t>
         </is>
       </c>
-      <c r="C47" s="35" t="n">
+      <c r="C47" s="34" t="n">
         <v>108</v>
       </c>
-      <c r="D47" s="35" t="n">
+      <c r="D47" s="34" t="n">
         <v>152</v>
       </c>
-      <c r="E47" s="45" t="inlineStr">
+      <c r="E47" s="44" t="inlineStr">
         <is>
           <t>71.1%</t>
         </is>
       </c>
-      <c r="F47" s="35" t="n">
+      <c r="F47" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="35" t="n">
+      <c r="G47" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H47" s="45" t="inlineStr">
+      <c r="H47" s="44" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="I47" s="35" t="n">
+      <c r="I47" s="34" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>mentor.entity</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>Sender</t>
         </is>
       </c>
-      <c r="C48" s="32" t="n">
+      <c r="C48" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D48" s="32" t="n">
+      <c r="D48" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="E48" s="43" t="inlineStr">
+      <c r="E48" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F48" s="32" t="n">
+      <c r="F48" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="32" t="n">
+      <c r="G48" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="44" t="inlineStr">
+      <c r="H48" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I48" s="32" t="n">
+      <c r="I48" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>mentor.service</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>LlmClient</t>
         </is>
       </c>
-      <c r="C49" s="35" t="n">
+      <c r="C49" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="D49" s="35" t="n">
+      <c r="D49" s="34" t="n">
         <v>104</v>
       </c>
-      <c r="E49" s="42" t="inlineStr">
+      <c r="E49" s="41" t="inlineStr">
         <is>
           <t>8.7%</t>
         </is>
       </c>
-      <c r="F49" s="35" t="n">
+      <c r="F49" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="35" t="n">
+      <c r="G49" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="42" t="inlineStr">
+      <c r="H49" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I49" s="35" t="n">
+      <c r="I49" s="34" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>mentor.service</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>MentorService</t>
         </is>
       </c>
-      <c r="C50" s="32" t="n">
+      <c r="C50" s="31" t="n">
         <v>175</v>
       </c>
-      <c r="D50" s="32" t="n">
+      <c r="D50" s="31" t="n">
         <v>175</v>
       </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F50" s="32" t="n">
+      <c r="F50" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="G50" s="32" t="n">
+      <c r="G50" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="H50" s="43" t="inlineStr">
+      <c r="H50" s="42" t="inlineStr">
         <is>
           <t>87.5%</t>
         </is>
       </c>
-      <c r="I50" s="32" t="n">
+      <c r="I50" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t>onboarding.controller</t>
         </is>
       </c>
-      <c r="B51" s="33" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>OnboardingController</t>
         </is>
       </c>
-      <c r="C51" s="35" t="n">
+      <c r="C51" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="D51" s="35" t="n">
+      <c r="D51" s="34" t="n">
         <v>295</v>
       </c>
-      <c r="E51" s="42" t="inlineStr">
+      <c r="E51" s="41" t="inlineStr">
         <is>
           <t>4.4%</t>
         </is>
       </c>
-      <c r="F51" s="35" t="n">
+      <c r="F51" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="35" t="n">
+      <c r="G51" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="H51" s="42" t="inlineStr">
+      <c r="H51" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I51" s="35" t="n">
+      <c r="I51" s="34" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>onboarding.service</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>OnboardingService</t>
         </is>
       </c>
-      <c r="C52" s="32" t="n">
+      <c r="C52" s="31" t="n">
         <v>99</v>
       </c>
-      <c r="D52" s="32" t="n">
+      <c r="D52" s="31" t="n">
         <v>99</v>
       </c>
-      <c r="E52" s="43" t="inlineStr">
+      <c r="E52" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F52" s="32" t="n">
+      <c r="F52" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G52" s="32" t="n">
+      <c r="G52" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="H52" s="45" t="inlineStr">
+      <c r="H52" s="44" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I52" s="32" t="n">
+      <c r="I52" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>onboarding.service</t>
         </is>
       </c>
-      <c r="B53" s="33" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>TranscriptAnalysisService</t>
         </is>
       </c>
-      <c r="C53" s="35" t="n">
+      <c r="C53" s="34" t="n">
         <v>95</v>
       </c>
-      <c r="D53" s="35" t="n">
+      <c r="D53" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="E53" s="43" t="inlineStr">
+      <c r="E53" s="42" t="inlineStr">
         <is>
           <t>95.0%</t>
         </is>
       </c>
-      <c r="F53" s="35" t="n">
+      <c r="F53" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="G53" s="35" t="n">
+      <c r="G53" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H53" s="43" t="inlineStr">
+      <c r="H53" s="42" t="inlineStr">
         <is>
           <t>83.3%</t>
         </is>
       </c>
-      <c r="I53" s="35" t="n">
+      <c r="I53" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>portfolio.controller</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>PortfolioController</t>
         </is>
       </c>
-      <c r="C54" s="32" t="n">
+      <c r="C54" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="D54" s="32" t="n">
+      <c r="D54" s="31" t="n">
         <v>98</v>
       </c>
-      <c r="E54" s="45" t="inlineStr">
+      <c r="E54" s="44" t="inlineStr">
         <is>
           <t>52.0%</t>
         </is>
       </c>
-      <c r="F54" s="32" t="n">
+      <c r="F54" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="32" t="n">
+      <c r="G54" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H54" s="43" t="inlineStr">
+      <c r="H54" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I54" s="32" t="n">
+      <c r="I54" s="31" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t>portfolio.controller</t>
         </is>
       </c>
-      <c r="B55" s="33" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>PublicPortfolioController</t>
         </is>
       </c>
-      <c r="C55" s="35" t="n">
+      <c r="C55" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="D55" s="35" t="n">
+      <c r="D55" s="34" t="n">
         <v>53</v>
       </c>
-      <c r="E55" s="43" t="inlineStr">
+      <c r="E55" s="42" t="inlineStr">
         <is>
           <t>88.7%</t>
         </is>
       </c>
-      <c r="F55" s="35" t="n">
+      <c r="F55" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="35" t="n">
+      <c r="G55" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="46" t="inlineStr">
+      <c r="H55" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I55" s="35" t="n">
+      <c r="I55" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="inlineStr">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>portfolio.dto</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>OwnerInfoDTO</t>
         </is>
       </c>
-      <c r="C56" s="32" t="n">
+      <c r="C56" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D56" s="32" t="n">
+      <c r="D56" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="E56" s="43" t="inlineStr">
+      <c r="E56" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F56" s="32" t="n">
+      <c r="F56" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="32" t="n">
+      <c r="G56" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="44" t="inlineStr">
+      <c r="H56" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I56" s="32" t="n">
+      <c r="I56" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+      <c r="A57" s="33" t="inlineStr">
         <is>
           <t>portfolio.entity</t>
         </is>
       </c>
-      <c r="B57" s="33" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>ProjectRepository</t>
         </is>
       </c>
-      <c r="C57" s="35" t="n">
+      <c r="C57" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="D57" s="35" t="n">
+      <c r="D57" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="E57" s="43" t="inlineStr">
+      <c r="E57" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F57" s="35" t="n">
+      <c r="F57" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="35" t="n">
+      <c r="G57" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="46" t="inlineStr">
+      <c r="H57" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I57" s="35" t="n">
+      <c r="I57" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>portfolio.service</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>PortfolioService</t>
         </is>
       </c>
-      <c r="C58" s="32" t="n">
+      <c r="C58" s="31" t="n">
         <v>409</v>
       </c>
-      <c r="D58" s="32" t="n">
+      <c r="D58" s="31" t="n">
         <v>431</v>
       </c>
-      <c r="E58" s="43" t="inlineStr">
+      <c r="E58" s="42" t="inlineStr">
         <is>
           <t>94.9%</t>
         </is>
       </c>
-      <c r="F58" s="32" t="n">
+      <c r="F58" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="G58" s="32" t="n">
+      <c r="G58" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="H58" s="45" t="inlineStr">
+      <c r="H58" s="44" t="inlineStr">
         <is>
           <t>77.5%</t>
         </is>
       </c>
-      <c r="I58" s="32" t="n">
+      <c r="I58" s="31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="A59" s="33" t="inlineStr">
         <is>
           <t>profile.controller</t>
         </is>
       </c>
-      <c r="B59" s="33" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>ProfileController</t>
         </is>
       </c>
-      <c r="C59" s="35" t="n">
+      <c r="C59" s="34" t="n">
         <v>148</v>
       </c>
-      <c r="D59" s="35" t="n">
+      <c r="D59" s="34" t="n">
         <v>149</v>
       </c>
-      <c r="E59" s="43" t="inlineStr">
+      <c r="E59" s="42" t="inlineStr">
         <is>
           <t>99.3%</t>
         </is>
       </c>
-      <c r="F59" s="35" t="n">
+      <c r="F59" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="G59" s="35" t="n">
+      <c r="G59" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H59" s="45" t="inlineStr">
+      <c r="H59" s="44" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I59" s="35" t="n">
+      <c r="I59" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>profile.service</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>ProfileService</t>
         </is>
       </c>
-      <c r="C60" s="32" t="n">
+      <c r="C60" s="31" t="n">
         <v>125</v>
       </c>
-      <c r="D60" s="32" t="n">
+      <c r="D60" s="31" t="n">
         <v>125</v>
       </c>
-      <c r="E60" s="43" t="inlineStr">
+      <c r="E60" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F60" s="32" t="n">
+      <c r="F60" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="G60" s="32" t="n">
+      <c r="G60" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="H60" s="43" t="inlineStr">
+      <c r="H60" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I60" s="32" t="n">
+      <c r="I60" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B61" s="33" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>RoadmapController</t>
         </is>
       </c>
-      <c r="C61" s="35" t="n">
+      <c r="C61" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="35" t="n">
+      <c r="D61" s="34" t="n">
         <v>53</v>
       </c>
-      <c r="E61" s="42" t="inlineStr">
+      <c r="E61" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F61" s="35" t="n">
+      <c r="F61" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="35" t="n">
+      <c r="G61" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="46" t="inlineStr">
+      <c r="H61" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I61" s="35" t="n">
+      <c r="I61" s="34" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31" t="inlineStr">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>RoadmapPageController</t>
         </is>
       </c>
-      <c r="C62" s="32" t="n">
+      <c r="C62" s="31" t="n">
         <v>242</v>
       </c>
-      <c r="D62" s="32" t="n">
+      <c r="D62" s="31" t="n">
         <v>259</v>
       </c>
-      <c r="E62" s="43" t="inlineStr">
+      <c r="E62" s="42" t="inlineStr">
         <is>
           <t>93.4%</t>
         </is>
       </c>
-      <c r="F62" s="32" t="n">
+      <c r="F62" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="G62" s="32" t="n">
+      <c r="G62" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="H62" s="45" t="inlineStr">
+      <c r="H62" s="44" t="inlineStr">
         <is>
           <t>76.5%</t>
         </is>
       </c>
-      <c r="I62" s="32" t="n">
+      <c r="I62" s="31" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="A63" s="33" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B63" s="33" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>SkillGapController</t>
         </is>
       </c>
-      <c r="C63" s="35" t="n">
+      <c r="C63" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="35" t="n">
+      <c r="D63" s="34" t="n">
         <v>66</v>
       </c>
-      <c r="E63" s="42" t="inlineStr">
+      <c r="E63" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F63" s="35" t="n">
+      <c r="F63" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="35" t="n">
+      <c r="G63" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="H63" s="41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I63" s="35" t="n">
+      <c r="I63" s="34" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>roadmap.controller</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>SkillGapPageController</t>
         </is>
       </c>
-      <c r="C64" s="32" t="n">
+      <c r="C64" s="31" t="n">
         <v>241</v>
       </c>
-      <c r="D64" s="32" t="n">
+      <c r="D64" s="31" t="n">
         <v>249</v>
       </c>
-      <c r="E64" s="43" t="inlineStr">
+      <c r="E64" s="42" t="inlineStr">
         <is>
           <t>96.8%</t>
         </is>
       </c>
-      <c r="F64" s="32" t="n">
+      <c r="F64" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="32" t="n">
+      <c r="G64" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="H64" s="45" t="inlineStr">
+      <c r="H64" s="44" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I64" s="32" t="n">
+      <c r="I64" s="31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>roadmap.dto</t>
         </is>
       </c>
-      <c r="B65" s="33" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>RoadmapTemplateDTO</t>
         </is>
       </c>
-      <c r="C65" s="35" t="n">
+      <c r="C65" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="D65" s="35" t="n">
+      <c r="D65" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E65" s="43" t="inlineStr">
+      <c r="E65" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F65" s="35" t="n">
+      <c r="F65" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="35" t="n">
+      <c r="G65" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="46" t="inlineStr">
+      <c r="H65" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I65" s="35" t="n">
+      <c r="I65" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31" t="inlineStr">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>roadmap.dto</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>SkillGapReportDTO</t>
         </is>
       </c>
-      <c r="C66" s="32" t="n">
+      <c r="C66" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="D66" s="32" t="n">
+      <c r="D66" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="E66" s="43" t="inlineStr">
+      <c r="E66" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F66" s="32" t="n">
+      <c r="F66" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="32" t="n">
+      <c r="G66" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="44" t="inlineStr">
+      <c r="H66" s="43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I66" s="32" t="n">
+      <c r="I66" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="34" t="inlineStr">
+      <c r="A67" s="33" t="inlineStr">
         <is>
           <t>roadmap.entity</t>
         </is>
       </c>
-      <c r="B67" s="33" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>ProgressStatus</t>
         </is>
       </c>
-      <c r="C67" s="35" t="n">
+      <c r="C67" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="D67" s="35" t="n">
+      <c r="D67" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="E67" s="43" t="inlineStr">
+      <c r="E67" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F67" s="35" t="n">
+      <c r="F67" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="35" t="n">
+      <c r="G67" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="46" t="inlineStr">
+      <c r="H67" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I67" s="35" t="n">
+      <c r="I67" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>PdfService</t>
         </is>
       </c>
-      <c r="C68" s="32" t="n">
+      <c r="C68" s="31" t="n">
         <v>368</v>
       </c>
-      <c r="D68" s="32" t="n">
+      <c r="D68" s="31" t="n">
         <v>384</v>
       </c>
-      <c r="E68" s="43" t="inlineStr">
+      <c r="E68" s="42" t="inlineStr">
         <is>
           <t>95.8%</t>
         </is>
       </c>
-      <c r="F68" s="32" t="n">
+      <c r="F68" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="G68" s="32" t="n">
+      <c r="G68" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="H68" s="43" t="inlineStr">
+      <c r="H68" s="42" t="inlineStr">
         <is>
           <t>85.7%</t>
         </is>
       </c>
-      <c r="I68" s="32" t="n">
+      <c r="I68" s="31" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="34" t="inlineStr">
+      <c r="A69" s="33" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B69" s="33" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>ProgressService</t>
         </is>
       </c>
-      <c r="C69" s="35" t="n">
+      <c r="C69" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="D69" s="35" t="n">
+      <c r="D69" s="34" t="n">
         <v>97</v>
       </c>
-      <c r="E69" s="43" t="inlineStr">
+      <c r="E69" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F69" s="35" t="n">
+      <c r="F69" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="G69" s="35" t="n">
+      <c r="G69" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="H69" s="43" t="inlineStr">
+      <c r="H69" s="42" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I69" s="35" t="n">
+      <c r="I69" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="31" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>RoadmapService</t>
         </is>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C70" s="31" t="n">
         <v>439</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D70" s="31" t="n">
         <v>445</v>
       </c>
-      <c r="E70" s="43" t="inlineStr">
+      <c r="E70" s="42" t="inlineStr">
         <is>
           <t>98.7%</t>
         </is>
       </c>
-      <c r="F70" s="32" t="n">
+      <c r="F70" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="G70" s="32" t="n">
+      <c r="G70" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="H70" s="43" t="inlineStr">
+      <c r="H70" s="42" t="inlineStr">
         <is>
           <t>97.6%</t>
         </is>
       </c>
-      <c r="I70" s="32" t="n">
+      <c r="I70" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>roadmap.service</t>
         </is>
       </c>
-      <c r="B71" s="33" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>SkillGapService</t>
         </is>
       </c>
-      <c r="C71" s="35" t="n">
+      <c r="C71" s="34" t="n">
         <v>404</v>
       </c>
-      <c r="D71" s="35" t="n">
+      <c r="D71" s="34" t="n">
         <v>418</v>
       </c>
-      <c r="E71" s="43" t="inlineStr">
+      <c r="E71" s="42" t="inlineStr">
         <is>
           <t>96.7%</t>
         </is>
       </c>
-      <c r="F71" s="35" t="n">
+      <c r="F71" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="35" t="n">
+      <c r="G71" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="H71" s="45" t="inlineStr">
+      <c r="H71" s="44" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I71" s="35" t="n">
+      <c r="I71" s="34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B73" s="47" t="n"/>
-      <c r="C73" s="29" t="n">
+      <c r="B73" s="46" t="n"/>
+      <c r="C73" s="28" t="n">
         <v>5798</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="28" t="n">
         <v>7622</v>
       </c>
-      <c r="E73" s="48" t="inlineStr">
+      <c r="E73" s="47" t="inlineStr">
         <is>
           <t>76.1%</t>
         </is>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F73" s="28" t="n">
         <v>369</v>
       </c>
-      <c r="G73" s="29" t="n">
+      <c r="G73" s="28" t="n">
         <v>547</v>
       </c>
-      <c r="H73" s="48" t="inlineStr">
+      <c r="H73" s="47" t="inlineStr">
         <is>
           <t>67.5%</t>
         </is>
       </c>
-      <c r="I73" s="29" t="n">
+      <c r="I73" s="28" t="n">
         <v>390</v>
       </c>
     </row>
